--- a/variables_ecocardio.xlsx
+++ b/variables_ecocardio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvanomarbalderamoreno/EcoCardioNet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvanomarbalderamoreno/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64B3080-02FD-B64B-8A66-24458A7F9A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BA4D9B-E6CF-7B4F-A895-428B0BBBAC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12060" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4720" yWindow="760" windowWidth="29400" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="461">
   <si>
     <t>Codigo</t>
   </si>
@@ -64,6 +64,9 @@
     <t>RAIZ_AORTICA</t>
   </si>
   <si>
+    <t>Ventrículo Derech. E Izq.</t>
+  </si>
+  <si>
     <t>Raíz Aórtica</t>
   </si>
   <si>
@@ -103,9 +106,6 @@
     <t>DIAMETRO_AI_2D</t>
   </si>
   <si>
-    <t>Dm AI (2D)</t>
-  </si>
-  <si>
     <t>Diámetro de la aurícula izquierda medido en 2D</t>
   </si>
   <si>
@@ -115,21 +115,21 @@
     <t>VOLUMEN_AI</t>
   </si>
   <si>
-    <t>Volumen de AI</t>
-  </si>
-  <si>
     <t>Volumen indexado o absoluto de la aurícula izquierda</t>
   </si>
   <si>
+    <t>mL o mL/m²</t>
+  </si>
+  <si>
     <t>&lt; 34</t>
   </si>
   <si>
+    <t>SI</t>
+  </si>
+  <si>
     <t>GRADO_DILATACION_AI</t>
   </si>
   <si>
-    <t>Grado Dilatación de AI</t>
-  </si>
-  <si>
     <t>Categorización según volumen de AI (normal ≤34, leve &gt;34-40, moderado 41-48 y severa &gt;48)</t>
   </si>
   <si>
@@ -148,9 +148,6 @@
     <t>STRAIN_AI_LASR</t>
   </si>
   <si>
-    <t>Strain AI (LASr)</t>
-  </si>
-  <si>
     <t>Strain de reservorio de la aurícula izquierda</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>AREA_AD_4_CAMARAS</t>
   </si>
   <si>
-    <t>Área AD (4 cámaras)</t>
-  </si>
-  <si>
     <t>Área de la aurícula derecha en vista de 4 cámaras</t>
   </si>
   <si>
@@ -187,21 +181,18 @@
     <t>RAIZ_AORTICA_INDEXADA</t>
   </si>
   <si>
-    <t>R. Ao index</t>
-  </si>
-  <si>
     <t xml:space="preserve">Raíz aórtica indexada a superficie corporal (Raiz aórtica/área de superficie corporal (peso y talla) </t>
   </si>
   <si>
+    <t>cm/m² --&gt; Fórmula Dubois</t>
+  </si>
+  <si>
     <t>1,5–2</t>
   </si>
   <si>
     <t>AORTA_ASCENDENTE</t>
   </si>
   <si>
-    <t>Ao Ascendente</t>
-  </si>
-  <si>
     <t>Diámetro de la aorta ascendente</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>AORTA_ASCENDENTE_INDEXADA</t>
   </si>
   <si>
-    <t>Ao Asc Index</t>
-  </si>
-  <si>
     <t>Aorta ascendente indexada a superficie corporal</t>
   </si>
   <si>
@@ -226,9 +214,6 @@
     <t>ARCO_AORTICO</t>
   </si>
   <si>
-    <t>Arco Aórtico</t>
-  </si>
-  <si>
     <t>Diámetro del arco aórtico</t>
   </si>
   <si>
@@ -250,9 +235,6 @@
     <t>DIAMETRO_VI_DIASTOLICO</t>
   </si>
   <si>
-    <t>DVId</t>
-  </si>
-  <si>
     <t>Diámetro ventricular izquierdo en diástole</t>
   </si>
   <si>
@@ -286,9 +268,6 @@
     <t>DIAMETRO_VI_SISTOLICO</t>
   </si>
   <si>
-    <t>DVIs</t>
-  </si>
-  <si>
     <t>Diámetro ventricular izquierdo en sístole</t>
   </si>
   <si>
@@ -313,6 +292,9 @@
     <t>Fracción de eyección del ventrículo izquierdo</t>
   </si>
   <si>
+    <t>% (Fórmula Simpson, 2D, Teicholz, otros)</t>
+  </si>
+  <si>
     <t>Normal;Disfunción leve;Disfunción moderada;Disfunción severa</t>
   </si>
   <si>
@@ -325,9 +307,6 @@
     <t>FRACCION_ACORTAMIENTO</t>
   </si>
   <si>
-    <t>% F Acort.</t>
-  </si>
-  <si>
     <t>Fracción de acortamiento ventricular izquierda</t>
   </si>
   <si>
@@ -358,15 +337,15 @@
     <t>Categorización de masa VI (normal, leve, moderada, severa) según sexo</t>
   </si>
   <si>
+    <t xml:space="preserve">Cualitativo </t>
+  </si>
+  <si>
     <t>Normal: H ≤115 / M ≤95 g/m² | Leve: H 116–131 / M 96–108 g/m² | Moderada: H 132–148 / M 109–121 g/m² | Severa: H &gt;148 / M &gt;121 g/m²</t>
   </si>
   <si>
     <t>MASA_VI_INDEXADA</t>
   </si>
   <si>
-    <t>Masa/index</t>
-  </si>
-  <si>
     <t>Masa ventricular izquierda indexada a superficie corporal</t>
   </si>
   <si>
@@ -397,9 +376,6 @@
     <t>VOLUMEN_FIN_DIASTOLE_VI</t>
   </si>
   <si>
-    <t>VFD</t>
-  </si>
-  <si>
     <t>Volumen de fin de diástole del ventrículo izquierdo</t>
   </si>
   <si>
@@ -412,9 +388,6 @@
     <t>VOLUMEN_FIN_DIASTOLE_VI_INDEXADO</t>
   </si>
   <si>
-    <t>VFD indexado</t>
-  </si>
-  <si>
     <t>Volumen de fin de diástole indexado</t>
   </si>
   <si>
@@ -424,9 +397,6 @@
     <t>VOLUMEN_FIN_SISTOLE_VI</t>
   </si>
   <si>
-    <t>VFS</t>
-  </si>
-  <si>
     <t>Volumen de fin de sístole del ventrículo izquierdo</t>
   </si>
   <si>
@@ -436,9 +406,6 @@
     <t>VOLUMEN_FIN_SISTOLE_VI_INDEXADO</t>
   </si>
   <si>
-    <t>VFS indexado</t>
-  </si>
-  <si>
     <t>Volumen de fin de sístole indexado</t>
   </si>
   <si>
@@ -448,9 +415,6 @@
     <t>VOLUMEN_LATIDO</t>
   </si>
   <si>
-    <t>Volumen latido</t>
-  </si>
-  <si>
     <t>Volumen sistólico (stroke volume)</t>
   </si>
   <si>
@@ -472,9 +436,6 @@
     <t>STRAIN_LONGITUDINAL_GLOBAL_VI</t>
   </si>
   <si>
-    <t>Strain VI (GLS)</t>
-  </si>
-  <si>
     <t>Strain longitudinal global del ventrículo izquierdo (Longitudinal, Radial, Circunferencial, otros)</t>
   </si>
   <si>
@@ -490,9 +451,6 @@
     <t>FEVI_POR_STRAIN</t>
   </si>
   <si>
-    <t>FEVI Strain</t>
-  </si>
-  <si>
     <t>Fracción de eyección derivada por strain</t>
   </si>
   <si>
@@ -523,6 +481,9 @@
     <t xml:space="preserve">Presencia de Derrame Pericardico (DP) (Sin derrame [0], leve [1-10], moderado [10-20], severo [&gt;20 mm]) </t>
   </si>
   <si>
+    <t>Cualitativa en base a medida</t>
+  </si>
+  <si>
     <t>Sin derrame;Leve;Moderado;Severo</t>
   </si>
   <si>
@@ -532,12 +493,12 @@
     <t>TAPONAMIENTO_CARDIACO</t>
   </si>
   <si>
-    <t>Taponamiento</t>
-  </si>
-  <si>
     <t>DP con compromiso hemodinámico (activar solo si es DP es severo)</t>
   </si>
   <si>
+    <t>Cualitativo (Si/No)</t>
+  </si>
+  <si>
     <t>No;Sí</t>
   </si>
   <si>
@@ -547,9 +508,6 @@
     <t>DIAMETRO_VD_BASAL</t>
   </si>
   <si>
-    <t>Diám. VD basal</t>
-  </si>
-  <si>
     <t>Diámetro basal del ventrículo derecho</t>
   </si>
   <si>
@@ -559,9 +517,6 @@
     <t>DIAMETRO_VD_MEDIO</t>
   </si>
   <si>
-    <t>Diám. VD medio</t>
-  </si>
-  <si>
     <t>Diámetro medio del ventrículo derecho</t>
   </si>
   <si>
@@ -580,9 +535,6 @@
     <t>ONDA_S_PRIMA</t>
   </si>
   <si>
-    <t>Onda S'</t>
-  </si>
-  <si>
     <t>Velocidad sistólica del anillo tricuspídeo por Doppler tisular</t>
   </si>
   <si>
@@ -601,6 +553,9 @@
     <t>Eficiciencia eyectiva del VD contra preisón pulmonar</t>
   </si>
   <si>
+    <t>mm/Hg - %</t>
+  </si>
+  <si>
     <t>Normal: ≥0,31 | Alterado: &lt;0,31</t>
   </si>
   <si>
@@ -610,9 +565,6 @@
     <t>Valvula mitral</t>
   </si>
   <si>
-    <t>E mitral</t>
-  </si>
-  <si>
     <t>Velocidad máxima de la onda E del flujo transmitral</t>
   </si>
   <si>
@@ -625,9 +577,6 @@
     <t>TIEMPO_DESACELERACION_MITRAL</t>
   </si>
   <si>
-    <t>TD</t>
-  </si>
-  <si>
     <t>Tiempo de desaceleración de la onda E</t>
   </si>
   <si>
@@ -640,9 +589,6 @@
     <t>ONDA_A_MITRAL</t>
   </si>
   <si>
-    <t>A mitral</t>
-  </si>
-  <si>
     <t>Velocidad máxima de la onda A del flujo transmitral</t>
   </si>
   <si>
@@ -703,9 +649,6 @@
     <t>PROTESIS_MITRAL</t>
   </si>
   <si>
-    <t>Prótesis mitral</t>
-  </si>
-  <si>
     <t>Presencia y tipo de prótesis mitral (Biológica, Mecanisca, TAVI, Plastia)</t>
   </si>
   <si>
@@ -721,9 +664,6 @@
     <t>GRADIENTE_MEDIO_MITRAL</t>
   </si>
   <si>
-    <t>Gradiente medio mitral</t>
-  </si>
-  <si>
     <t>Gradiente medio transvalvular mitral</t>
   </si>
   <si>
@@ -775,9 +715,6 @@
     <t>MOVILIDAD_VELOS_MITRALES</t>
   </si>
   <si>
-    <t>Mov Ve</t>
-  </si>
-  <si>
     <t>Movilidad de velos mitrales (1, 2, 3, 4)</t>
   </si>
   <si>
@@ -877,9 +814,6 @@
     <t>VOLUMEN_REGURGITANTE_MITRAL</t>
   </si>
   <si>
-    <t>Vol Rg mitral</t>
-  </si>
-  <si>
     <t>Volumen regurgitante mitral</t>
   </si>
   <si>
@@ -916,9 +850,6 @@
     <t>GRADIENTE_MEDIO_AORTICO</t>
   </si>
   <si>
-    <t>Gdte medio Ao</t>
-  </si>
-  <si>
     <t>Gradiente medio transaórtico</t>
   </si>
   <si>
@@ -928,9 +859,6 @@
     <t>VTI_AORTICO</t>
   </si>
   <si>
-    <t>VTI VAo</t>
-  </si>
-  <si>
     <t>Integral velocidad-tiempo aórtica</t>
   </si>
   <si>
@@ -955,9 +883,6 @@
     <t>VELOCIDAD_MAXIMA_TSVI</t>
   </si>
   <si>
-    <t>Vmax TSVI</t>
-  </si>
-  <si>
     <t>Velocidad máxima en el TSVI</t>
   </si>
   <si>
@@ -1066,9 +991,6 @@
     <t>FLUJO_TRANSVALVULAR_AORTICO</t>
   </si>
   <si>
-    <t>Flujo transvalvular</t>
-  </si>
-  <si>
     <t>Flujo a través de la válvula aórtica</t>
   </si>
   <si>
@@ -1135,9 +1057,6 @@
     <t>VENA_CONTRACTA_AORTICA</t>
   </si>
   <si>
-    <t>VC aórtica</t>
-  </si>
-  <si>
     <t>Vena contracta de insuficiencia aórtica</t>
   </si>
   <si>
@@ -1186,9 +1105,6 @@
     <t>VELOCIDAD_MAXIMA_IT</t>
   </si>
   <si>
-    <t>Vel. máx. IT</t>
-  </si>
-  <si>
     <t>Velocidad máxima del jet de insuficiencia tricuspídea</t>
   </si>
   <si>
@@ -1198,9 +1114,6 @@
     <t>GRADIENTE_MAXIMO_IT</t>
   </si>
   <si>
-    <t>Gdte máx. IT</t>
-  </si>
-  <si>
     <t>Gradiente máximo derivado de la insuficiencia tricuspídea</t>
   </si>
   <si>
@@ -1210,9 +1123,6 @@
     <t>DIAMETRO_VCI</t>
   </si>
   <si>
-    <t>VCI</t>
-  </si>
-  <si>
     <t>Diámetro de la vena cava inferior (No dilatada y colapsa &gt;50% (5), No dilatada y colapsa &lt;50% (10%), Dilatada y colapsa &lt;50% (15) y Dilatada y sin colapso (20))</t>
   </si>
   <si>
@@ -1309,9 +1219,6 @@
     <t>VELOCIDAD_PICO_PULMONAR</t>
   </si>
   <si>
-    <t>V Peak pulmonar</t>
-  </si>
-  <si>
     <t>Velocidad máxima transvalvular pulmonar</t>
   </si>
   <si>
@@ -1336,9 +1243,6 @@
     <t>GRADO_REFLUJO_PULMONAR</t>
   </si>
   <si>
-    <t>Reflujo pulmonar</t>
-  </si>
-  <si>
     <t>Grado de insuficiencia pulmonar  (No observo, Mínima, Leve, Leva a Moderada, Moderada, Moderada a severa, Severa y Masiva)</t>
   </si>
   <si>
@@ -1366,32 +1270,149 @@
     <t>Resistencia vascular pulmonar estimada</t>
   </si>
   <si>
+    <t>Unidades Wood (UW)</t>
+  </si>
+  <si>
     <t>Normal;Elevada;Severamente elevada</t>
   </si>
   <si>
     <t>Normal: &lt;3 UW | Elevada: 3–5 UW | Severamente elevada: &gt;5 UW</t>
   </si>
   <si>
-    <t>UW</t>
-  </si>
-  <si>
-    <t>mm/Hg</t>
-  </si>
-  <si>
-    <t>Aorta y Auriculas</t>
-  </si>
-  <si>
-    <t>Ventrículo Izquierdo</t>
-  </si>
-  <si>
-    <t>Ventrículo Derecho</t>
+    <t>Diametro AI</t>
+  </si>
+  <si>
+    <t>Vol. indexado AI</t>
+  </si>
+  <si>
+    <t>Área AD</t>
+  </si>
+  <si>
+    <t>Raíz Aórtica/ASC</t>
+  </si>
+  <si>
+    <t>Aorta ascendente</t>
+  </si>
+  <si>
+    <t>Aorta ascend/ASC</t>
+  </si>
+  <si>
+    <t>Dimensión Diast. VI.</t>
+  </si>
+  <si>
+    <t>Dimensión. Sist. VI.</t>
+  </si>
+  <si>
+    <t>% Acortamiento</t>
+  </si>
+  <si>
+    <t>Frac. Eyección</t>
+  </si>
+  <si>
+    <t>Masa VI/ASC</t>
+  </si>
+  <si>
+    <t>Vol FinDias/Asc VI</t>
+  </si>
+  <si>
+    <t>Vol FinSist/Asc VI </t>
+  </si>
+  <si>
+    <t>Diam. basal VD</t>
+  </si>
+  <si>
+    <t>Diam. medio VD</t>
+  </si>
+  <si>
+    <t>Tapse</t>
+  </si>
+  <si>
+    <t>onda S'</t>
+  </si>
+  <si>
+    <t>T. D.</t>
+  </si>
+  <si>
+    <t>Onda A</t>
+  </si>
+  <si>
+    <t>Gdte medio</t>
+  </si>
+  <si>
+    <t>Grado Dilatación de AI-Auricula izquierda</t>
+  </si>
+  <si>
+    <t>FEVi Strain</t>
+  </si>
+  <si>
+    <t>Strain longitudinal</t>
+  </si>
+  <si>
+    <t>Strain AI</t>
+  </si>
+  <si>
+    <t>Arco aórtico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VFD - Volumen de fin de diastole </t>
+  </si>
+  <si>
+    <t>VFS - Volumen de fin de sistole</t>
+  </si>
+  <si>
+    <t>Vol Latido</t>
+  </si>
+  <si>
+    <t>PERICARDIO</t>
+  </si>
+  <si>
+    <t>taponamiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prótesis mitral - Protesis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movilidad </t>
+  </si>
+  <si>
+    <t>Vol Reg.</t>
+  </si>
+  <si>
+    <t>VTI</t>
+  </si>
+  <si>
+    <t>V. Max</t>
+  </si>
+  <si>
+    <t>Gradiente medio</t>
+  </si>
+  <si>
+    <t>vena contracta aórtica</t>
+  </si>
+  <si>
+    <t>flujo transvalvular</t>
+  </si>
+  <si>
+    <t>Vel. Maxima IT</t>
+  </si>
+  <si>
+    <t>Gdte maxima IT</t>
+  </si>
+  <si>
+    <t>Vena Cava Inf. </t>
+  </si>
+  <si>
+    <t>V. Max </t>
+  </si>
+  <si>
+    <t>Reflujo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1405,13 +1426,40 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1441,11 +1489,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1805,95 +1858,95 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>451</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
         <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1901,42 +1954,42 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
-        <v>126</v>
-      </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
         <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>451</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>438</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
@@ -1954,10 +2007,10 @@
         <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1965,502 +2018,502 @@
         <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>451</v>
-      </c>
-      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>44</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>45</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" t="s">
         <v>46</v>
-      </c>
-      <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D8" t="s">
         <v>48</v>
       </c>
-      <c r="B8" t="s">
-        <v>451</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>49</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>52</v>
-      </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
-        <v>451</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
         <v>54</v>
       </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
-        <v>451</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>60</v>
-      </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" t="s">
-        <v>451</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>65</v>
-      </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>451</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
+        <v>13</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>442</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>452</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>452</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
+        <v>13</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>424</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>452</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>452</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>452</v>
-      </c>
-      <c r="C17" t="s">
-        <v>87</v>
+        <v>13</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>452</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
+        <v>13</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>452</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
+        <v>13</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>427</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>452</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
+        <v>13</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>452</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
+        <v>13</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
-        <v>452</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
+        <v>13</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
         <v>37</v>
@@ -2469,2478 +2522,2478 @@
         <v>38</v>
       </c>
       <c r="H22" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>452</v>
-      </c>
-      <c r="C23" t="s">
-        <v>113</v>
+        <v>13</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>428</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
         <v>38</v>
       </c>
       <c r="H23" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="K23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>452</v>
-      </c>
-      <c r="C24" t="s">
-        <v>118</v>
+        <v>13</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s">
-        <v>452</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
+        <v>13</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B26" t="s">
-        <v>452</v>
-      </c>
-      <c r="C26" t="s">
-        <v>129</v>
+        <v>13</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>429</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
         <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="K26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>452</v>
-      </c>
-      <c r="C27" t="s">
-        <v>133</v>
+        <v>13</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>452</v>
-      </c>
-      <c r="C28" t="s">
-        <v>137</v>
+        <v>13</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>430</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
         <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="K28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>452</v>
-      </c>
-      <c r="C29" t="s">
-        <v>141</v>
+        <v>13</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>445</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E29" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B30" t="s">
-        <v>452</v>
-      </c>
-      <c r="C30" t="s">
-        <v>145</v>
+        <v>13</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
         <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
-        <v>452</v>
-      </c>
-      <c r="C31" t="s">
-        <v>149</v>
+        <v>13</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>440</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H31" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="I31" t="s">
+        <v>45</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" t="s">
         <v>46</v>
-      </c>
-      <c r="K31" t="s">
-        <v>19</v>
-      </c>
-      <c r="L31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B32" t="s">
-        <v>452</v>
-      </c>
-      <c r="C32" t="s">
-        <v>155</v>
+        <v>13</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>439</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H32" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="I32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" t="s">
         <v>46</v>
-      </c>
-      <c r="K32" t="s">
-        <v>19</v>
-      </c>
-      <c r="L32" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
-      </c>
-      <c r="C33" t="s">
-        <v>159</v>
+        <v>13</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="H33" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" t="s">
-        <v>164</v>
+        <v>13</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>228</v>
+        <v>152</v>
       </c>
       <c r="F34" t="s">
         <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="H34" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="K34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
-      </c>
-      <c r="C35" t="s">
-        <v>169</v>
+        <v>13</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>447</v>
       </c>
       <c r="D35" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="E35" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="F35" t="s">
         <v>37</v>
       </c>
       <c r="G35" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="H35" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="K35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>453</v>
-      </c>
-      <c r="C36" t="s">
-        <v>174</v>
+        <v>13</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>431</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H36" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="K36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s">
-        <v>453</v>
-      </c>
-      <c r="C37" t="s">
-        <v>178</v>
+        <v>13</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="D37" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H37" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B38" t="s">
-        <v>453</v>
-      </c>
-      <c r="C38" t="s">
-        <v>181</v>
+        <v>13</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>433</v>
       </c>
       <c r="D38" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H38" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="K38" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>453</v>
-      </c>
-      <c r="C39" t="s">
-        <v>185</v>
+        <v>13</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>434</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="E39" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H39" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="K39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B40" t="s">
-        <v>453</v>
-      </c>
-      <c r="C40" t="s">
-        <v>190</v>
+        <v>13</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="D40" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
-        <v>450</v>
+        <v>176</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H40" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
-      </c>
-      <c r="C41" t="s">
-        <v>195</v>
+        <v>179</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>382</v>
       </c>
       <c r="D41" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="K41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" t="s">
-        <v>200</v>
+        <v>179</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>435</v>
       </c>
       <c r="D42" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
-      </c>
-      <c r="C43" t="s">
-        <v>205</v>
+        <v>179</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>436</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E43" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H43" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="K43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B44" t="s">
-        <v>194</v>
-      </c>
-      <c r="C44" t="s">
-        <v>209</v>
+        <v>179</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="D44" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H44" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="K44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>194</v>
-      </c>
-      <c r="C45" t="s">
-        <v>213</v>
+        <v>179</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="D45" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H45" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="K45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
-      </c>
-      <c r="C46" t="s">
-        <v>217</v>
+        <v>179</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="D46" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="E46" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H46" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="K46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B47" t="s">
-        <v>194</v>
-      </c>
-      <c r="C47" t="s">
-        <v>221</v>
+        <v>179</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="D47" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="E47" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H47" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="K47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L47" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="B48" t="s">
-        <v>194</v>
-      </c>
-      <c r="C48" t="s">
-        <v>226</v>
+        <v>179</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>448</v>
       </c>
       <c r="D48" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="E48" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F48" t="s">
         <v>37</v>
       </c>
       <c r="G48" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="H48" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="K48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
-      </c>
-      <c r="C49" t="s">
-        <v>232</v>
+        <v>179</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>437</v>
       </c>
       <c r="D49" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="E49" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="H49" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="I49" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="K49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L49" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s">
-        <v>194</v>
-      </c>
-      <c r="C50" t="s">
-        <v>240</v>
+        <v>179</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="E50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
         <v>38</v>
       </c>
       <c r="H50" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="K50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
-      </c>
-      <c r="C51" t="s">
-        <v>244</v>
+        <v>179</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="D51" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="E51" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="H51" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="K51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s">
-        <v>194</v>
-      </c>
-      <c r="C52" t="s">
-        <v>250</v>
+        <v>179</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>449</v>
       </c>
       <c r="D52" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="E52" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="H52" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="K52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s">
-        <v>194</v>
-      </c>
-      <c r="C53" t="s">
-        <v>255</v>
+        <v>179</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>234</v>
       </c>
       <c r="D53" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="E53" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="H53" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="K53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s">
-        <v>194</v>
-      </c>
-      <c r="C54" t="s">
-        <v>258</v>
+        <v>179</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>237</v>
       </c>
       <c r="D54" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="E54" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="H54" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="K54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s">
-        <v>194</v>
-      </c>
-      <c r="C55" t="s">
-        <v>261</v>
+        <v>179</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="E55" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="H55" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="K55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="B56" t="s">
-        <v>194</v>
-      </c>
-      <c r="C56" t="s">
-        <v>264</v>
+        <v>179</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="D56" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="E56" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F56" t="s">
         <v>37</v>
       </c>
       <c r="G56" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="H56" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="K56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L56" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B57" t="s">
-        <v>194</v>
-      </c>
-      <c r="C57" t="s">
-        <v>270</v>
+        <v>179</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="D57" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G57" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H57" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="K57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s">
-        <v>194</v>
-      </c>
-      <c r="C58" t="s">
-        <v>275</v>
+        <v>179</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G58" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H58" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="I58" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="K58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L58" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="B59" t="s">
-        <v>194</v>
-      </c>
-      <c r="C59" t="s">
-        <v>280</v>
+        <v>179</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="D59" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="E59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H59" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="I59" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="K59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L59" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="B60" t="s">
-        <v>194</v>
-      </c>
-      <c r="C60" t="s">
-        <v>284</v>
+        <v>179</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>450</v>
       </c>
       <c r="D60" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="E60" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H60" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="K60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="B61" t="s">
-        <v>194</v>
-      </c>
-      <c r="C61" t="s">
-        <v>288</v>
+        <v>179</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>266</v>
       </c>
       <c r="D61" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H61" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="K61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="B62" t="s">
-        <v>292</v>
-      </c>
-      <c r="C62" t="s">
-        <v>293</v>
+        <v>270</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="D62" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="E62" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G62" t="s">
         <v>38</v>
       </c>
       <c r="H62" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="K62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="B63" t="s">
-        <v>292</v>
-      </c>
-      <c r="C63" t="s">
-        <v>297</v>
+        <v>270</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>453</v>
       </c>
       <c r="D63" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="E63" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G63" t="s">
         <v>38</v>
       </c>
       <c r="H63" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="K63" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B64" t="s">
-        <v>292</v>
-      </c>
-      <c r="C64" t="s">
-        <v>301</v>
+        <v>270</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>451</v>
       </c>
       <c r="D64" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="E64" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H64" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="I64" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="K64" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B65" t="s">
-        <v>292</v>
-      </c>
-      <c r="C65" t="s">
-        <v>306</v>
+        <v>270</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="D65" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="E65" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H65" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="K65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="B66" t="s">
-        <v>292</v>
-      </c>
-      <c r="C66" t="s">
-        <v>310</v>
+        <v>270</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>452</v>
       </c>
       <c r="D66" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="E66" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="K66" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="B67" t="s">
-        <v>292</v>
-      </c>
-      <c r="C67" t="s">
-        <v>314</v>
+        <v>270</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>289</v>
       </c>
       <c r="D67" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="E67" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H67" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="I67" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="K67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="B68" t="s">
-        <v>292</v>
-      </c>
-      <c r="C68" t="s">
-        <v>318</v>
+        <v>270</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>293</v>
       </c>
       <c r="D68" t="s">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="E68" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H68" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="K68" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B69" t="s">
-        <v>292</v>
-      </c>
-      <c r="C69" t="s">
-        <v>322</v>
+        <v>270</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>297</v>
       </c>
       <c r="D69" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="E69" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G69" t="s">
         <v>38</v>
       </c>
       <c r="H69" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="K69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="B70" t="s">
-        <v>292</v>
-      </c>
-      <c r="C70" t="s">
-        <v>326</v>
+        <v>270</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>301</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="E70" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H70" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="K70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="B71" t="s">
-        <v>292</v>
-      </c>
-      <c r="C71" t="s">
-        <v>330</v>
+        <v>270</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="E71" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="H71" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="K71" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="B72" t="s">
-        <v>292</v>
-      </c>
-      <c r="C72" t="s">
-        <v>335</v>
+        <v>270</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>310</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="E72" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G72" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="H72" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="K72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="B73" t="s">
-        <v>292</v>
-      </c>
-      <c r="C73" t="s">
-        <v>339</v>
+        <v>270</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="D73" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E73" t="s">
         <v>36</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G73" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="H73" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="K73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="B74" t="s">
-        <v>292</v>
-      </c>
-      <c r="C74" t="s">
-        <v>343</v>
+        <v>270</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>318</v>
       </c>
       <c r="D74" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="E74" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H74" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="K74" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="B75" t="s">
-        <v>292</v>
-      </c>
-      <c r="C75" t="s">
-        <v>347</v>
+        <v>270</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="D75" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="E75" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G75" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="H75" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="K75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="B76" t="s">
-        <v>292</v>
-      </c>
-      <c r="C76" t="s">
-        <v>353</v>
+        <v>270</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>327</v>
       </c>
       <c r="D76" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="E76" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G76" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="H76" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="K76" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="B77" t="s">
-        <v>292</v>
-      </c>
-      <c r="C77" t="s">
-        <v>359</v>
+        <v>270</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D77" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="E77" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F77" t="s">
         <v>37</v>
       </c>
       <c r="G77" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="H77" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="K77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="B78" t="s">
-        <v>292</v>
-      </c>
-      <c r="C78" t="s">
-        <v>362</v>
+        <v>270</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>336</v>
       </c>
       <c r="D78" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="E78" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F78" t="s">
         <v>37</v>
       </c>
       <c r="G78" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="H78" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="K78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="B79" t="s">
-        <v>292</v>
-      </c>
-      <c r="C79" t="s">
-        <v>366</v>
+        <v>270</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>340</v>
       </c>
       <c r="D79" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="E79" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F79" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G79" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H79" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="K79" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="B80" t="s">
-        <v>292</v>
-      </c>
-      <c r="C80" t="s">
-        <v>370</v>
+        <v>270</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>454</v>
       </c>
       <c r="D80" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="E80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H80" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="K80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="B81" t="s">
-        <v>292</v>
-      </c>
-      <c r="C81" t="s">
-        <v>374</v>
+        <v>270</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="D81" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="E81" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G81" t="s">
         <v>2</v>
       </c>
       <c r="H81" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="I81" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="K81" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L81" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="B82" t="s">
-        <v>292</v>
-      </c>
-      <c r="C82" t="s">
-        <v>378</v>
+        <v>270</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="D82" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="E82" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H82" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="I82" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="K82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L82" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="B83" t="s">
-        <v>382</v>
-      </c>
-      <c r="C83" t="s">
-        <v>383</v>
+        <v>355</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="D83" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="E83" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F83" t="s">
         <v>37</v>
       </c>
       <c r="G83" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="H83" t="s">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="K83" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L83" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="B84" t="s">
-        <v>382</v>
-      </c>
-      <c r="C84" t="s">
-        <v>387</v>
+        <v>355</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>456</v>
       </c>
       <c r="D84" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="E84" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G84" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="H84" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="K84" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="B85" t="s">
-        <v>382</v>
-      </c>
-      <c r="C85" t="s">
-        <v>391</v>
+        <v>355</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>457</v>
       </c>
       <c r="D85" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="E85" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="F85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G85" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H85" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="K85" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="B86" t="s">
-        <v>382</v>
-      </c>
-      <c r="C86" t="s">
-        <v>395</v>
+        <v>355</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>458</v>
       </c>
       <c r="D86" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="E86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G86" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="H86" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="K86" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="B87" t="s">
-        <v>382</v>
-      </c>
-      <c r="C87" t="s">
-        <v>400</v>
+        <v>355</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>370</v>
       </c>
       <c r="D87" t="s">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F87" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G87" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H87" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="K87" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="B88" t="s">
-        <v>382</v>
-      </c>
-      <c r="C88" t="s">
-        <v>404</v>
+        <v>355</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="D88" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="E88" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s">
         <v>38</v>
       </c>
       <c r="H88" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="K88" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L88" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
       <c r="B89" t="s">
-        <v>382</v>
-      </c>
-      <c r="C89" t="s">
-        <v>409</v>
+        <v>355</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="D89" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="E89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G89" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="H89" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="K89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L89" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="B90" t="s">
+        <v>355</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="C90" t="s">
-        <v>412</v>
-      </c>
       <c r="D90" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="E90" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F90" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H90" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="K90" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="B91" t="s">
-        <v>382</v>
-      </c>
-      <c r="C91" t="s">
-        <v>416</v>
+        <v>355</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="D91" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="E91" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="F91" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G91" t="s">
         <v>2</v>
       </c>
       <c r="H91" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="I91" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="K91" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L91" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="B92" t="s">
-        <v>382</v>
-      </c>
-      <c r="C92" t="s">
-        <v>419</v>
+        <v>355</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>389</v>
       </c>
       <c r="D92" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="E92" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F92" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G92" t="s">
         <v>2</v>
       </c>
       <c r="H92" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="K92" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="B93" t="s">
-        <v>423</v>
-      </c>
-      <c r="C93" t="s">
-        <v>424</v>
+        <v>393</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>394</v>
       </c>
       <c r="D93" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="E93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H93" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="K93" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="B94" t="s">
-        <v>423</v>
-      </c>
-      <c r="C94" t="s">
-        <v>428</v>
+        <v>393</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>459</v>
       </c>
       <c r="D94" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="E94" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F94" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H94" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="K94" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="B95" t="s">
-        <v>423</v>
-      </c>
-      <c r="C95" t="s">
-        <v>432</v>
+        <v>393</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>401</v>
       </c>
       <c r="D95" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="E95" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F95" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G95" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="H95" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="K95" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="B96" t="s">
-        <v>423</v>
-      </c>
-      <c r="C96" t="s">
-        <v>437</v>
+        <v>393</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="D96" t="s">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="E96" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F96" t="s">
         <v>37</v>
       </c>
       <c r="G96" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="H96" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="K96" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L96" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="B97" t="s">
-        <v>423</v>
-      </c>
-      <c r="C97" t="s">
-        <v>441</v>
+        <v>393</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>409</v>
       </c>
       <c r="D97" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="E97" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="F97" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H97" t="s">
-        <v>443</v>
+        <v>411</v>
       </c>
       <c r="I97" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="K97" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="B98" t="s">
-        <v>423</v>
-      </c>
-      <c r="C98" t="s">
-        <v>445</v>
+        <v>393</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>413</v>
       </c>
       <c r="D98" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="E98" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="F98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G98" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="H98" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="K98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
